--- a/easyeyes_materials/crowding_stationary_dynamic_flies_vertical.xlsx
+++ b/easyeyes_materials/crowding_stationary_dynamic_flies_vertical.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fh986/Documents/Github/crowded-dynamic-fixation/easyeyes_materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEBEF98F-2A1C-3A47-81C1-18F4D5D05E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2EC63E-7D36-3D47-A92A-19BEE57C6D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="20760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>_about</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>July 22nd, 2025</t>
+  </si>
+  <si>
+    <t>fontMaxPx</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -849,275 +852,275 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" t="s">
-        <v>29</v>
+        <v>67</v>
+      </c>
+      <c r="C15">
+        <v>800</v>
+      </c>
+      <c r="D15">
+        <v>800</v>
+      </c>
+      <c r="E15">
+        <v>800</v>
+      </c>
+      <c r="F15">
+        <v>800</v>
+      </c>
+      <c r="G15">
+        <v>800</v>
+      </c>
+      <c r="H15">
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>-0.25</v>
-      </c>
-      <c r="H20">
-        <v>-0.25</v>
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23">
-        <v>0.15</v>
-      </c>
-      <c r="D23">
-        <v>0.15</v>
-      </c>
-      <c r="E23">
-        <v>0.15</v>
-      </c>
-      <c r="F23">
-        <v>0.15</v>
-      </c>
-      <c r="G23">
-        <v>0.15</v>
-      </c>
-      <c r="H23">
-        <v>0.15</v>
+        <v>38</v>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" t="s">
-        <v>41</v>
-      </c>
-      <c r="H24" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="C24">
+        <v>0.15</v>
+      </c>
+      <c r="D24">
+        <v>0.15</v>
+      </c>
+      <c r="E24">
+        <v>0.15</v>
+      </c>
+      <c r="F24">
+        <v>0.15</v>
+      </c>
+      <c r="G24">
+        <v>0.15</v>
+      </c>
+      <c r="H24">
+        <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25">
-        <v>0.5</v>
-      </c>
-      <c r="D25">
-        <v>0.5</v>
-      </c>
-      <c r="E25">
-        <v>0.5</v>
-      </c>
-      <c r="F25">
-        <v>0.5</v>
-      </c>
-      <c r="G25">
-        <v>0.5</v>
-      </c>
-      <c r="H25">
-        <v>0.5</v>
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E26">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G26">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H26">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" t="b">
         <v>1</v>
@@ -1140,376 +1143,399 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30">
-        <v>1.25</v>
-      </c>
-      <c r="D30">
-        <v>1.25</v>
-      </c>
-      <c r="E30">
-        <v>1.25</v>
-      </c>
-      <c r="F30">
-        <v>1.25</v>
-      </c>
-      <c r="G30">
-        <v>1.25</v>
-      </c>
-      <c r="H30">
-        <v>1.25</v>
+        <v>46</v>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="F31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="G31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="H31">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="G32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
       <c r="H32">
-        <v>30</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="C33">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
+        <v>30</v>
+      </c>
+      <c r="H33">
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36">
-        <v>0.15</v>
-      </c>
-      <c r="D36">
-        <v>0.15</v>
-      </c>
-      <c r="E36">
-        <v>0.15</v>
-      </c>
-      <c r="F36">
-        <v>0.15</v>
-      </c>
-      <c r="G36">
-        <v>0.15</v>
-      </c>
-      <c r="H36">
-        <v>0.15</v>
+        <v>52</v>
+      </c>
+      <c r="C36" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" t="s">
-        <v>57</v>
-      </c>
-      <c r="G39" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>-10</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>-10</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>-10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41">
-        <v>0.02</v>
-      </c>
-      <c r="D41">
-        <v>0.02</v>
-      </c>
-      <c r="E41">
-        <v>0.02</v>
-      </c>
-      <c r="F41">
-        <v>0.02</v>
-      </c>
-      <c r="G41">
-        <v>0.02</v>
-      </c>
-      <c r="H41">
-        <v>0.02</v>
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" t="s">
+        <v>59</v>
+      </c>
+      <c r="G41" t="s">
+        <v>59</v>
+      </c>
+      <c r="H41" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="E42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E43" t="s">
-        <v>63</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43" t="s">
-        <v>63</v>
-      </c>
-      <c r="H43" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>3</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44">
-        <v>0.7</v>
-      </c>
-      <c r="D44">
-        <v>0.7</v>
-      </c>
-      <c r="E44">
-        <v>0.7</v>
-      </c>
-      <c r="F44">
-        <v>0.7</v>
-      </c>
-      <c r="G44">
-        <v>0.7</v>
-      </c>
-      <c r="H44">
-        <v>0.7</v>
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" t="s">
+        <v>63</v>
+      </c>
+      <c r="G44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45">
+        <v>0.7</v>
+      </c>
+      <c r="D45">
+        <v>0.7</v>
+      </c>
+      <c r="E45">
+        <v>0.7</v>
+      </c>
+      <c r="F45">
+        <v>0.7</v>
+      </c>
+      <c r="G45">
+        <v>0.7</v>
+      </c>
+      <c r="H45">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>65</v>
       </c>
-      <c r="C45">
+      <c r="C46">
         <v>40</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>40</v>
       </c>
-      <c r="E45">
+      <c r="E46">
         <v>40</v>
       </c>
-      <c r="F45">
+      <c r="F46">
         <v>40</v>
       </c>
-      <c r="G45">
+      <c r="G46">
         <v>40</v>
       </c>
-      <c r="H45">
+      <c r="H46">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H2 A4:H36 A3 C3:H3 A39:H45 A38:B38 A37:B37" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H2 A16:H37 A3 C3:H3 A40:H42 A38:B39 A44:H46 A43:B43 A4:H14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>